--- a/results/analysis/vuln_detection_comprehensive_analysis.xlsx
+++ b/results/analysis/vuln_detection_comprehensive_analysis.xlsx
@@ -891,16 +891,16 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>52.591</v>
+        <v>53.886</v>
       </c>
       <c r="I7" t="n">
-        <v>51.984</v>
+        <v>58.242</v>
       </c>
       <c r="J7" t="n">
-        <v>67.876</v>
+        <v>27.461</v>
       </c>
       <c r="K7" t="n">
-        <v>58.876</v>
+        <v>37.324</v>
       </c>
       <c r="L7" t="n">
         <v>3.08</v>
@@ -1159,16 +1159,16 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>52.591</v>
+        <v>54.922</v>
       </c>
       <c r="I11" t="n">
-        <v>52.358</v>
+        <v>55.135</v>
       </c>
       <c r="J11" t="n">
-        <v>57.513</v>
+        <v>52.85</v>
       </c>
       <c r="K11" t="n">
-        <v>54.815</v>
+        <v>53.968</v>
       </c>
       <c r="L11" t="n">
         <v>1.316</v>
@@ -1293,16 +1293,16 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>50.259</v>
+        <v>53.627</v>
       </c>
       <c r="I13" t="n">
-        <v>50.209</v>
+        <v>54.43</v>
       </c>
       <c r="J13" t="n">
-        <v>62.176</v>
+        <v>44.56</v>
       </c>
       <c r="K13" t="n">
-        <v>55.556</v>
+        <v>49.003</v>
       </c>
       <c r="L13" t="n">
         <v>1.235</v>
@@ -1494,16 +1494,16 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>52.591</v>
+        <v>52.332</v>
       </c>
       <c r="I16" t="n">
-        <v>51.984</v>
+        <v>54.639</v>
       </c>
       <c r="J16" t="n">
-        <v>67.876</v>
+        <v>27.461</v>
       </c>
       <c r="K16" t="n">
-        <v>58.876</v>
+        <v>36.552</v>
       </c>
       <c r="L16" t="n">
         <v>3.651</v>
@@ -1561,16 +1561,16 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>50.259</v>
+        <v>51.295</v>
       </c>
       <c r="I17" t="n">
-        <v>50.256</v>
+        <v>52.101</v>
       </c>
       <c r="J17" t="n">
-        <v>50.777</v>
+        <v>32.124</v>
       </c>
       <c r="K17" t="n">
-        <v>50.515</v>
+        <v>39.744</v>
       </c>
       <c r="L17" t="n">
         <v>2.849</v>
@@ -1634,10 +1634,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>53.35</v>
+        <v>54.3</v>
       </c>
       <c r="C2" t="n">
-        <v>50.44</v>
+        <v>49.21</v>
       </c>
       <c r="D2" t="n">
         <v>0.8</v>
@@ -1650,10 +1650,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>52.13</v>
+        <v>52.33</v>
       </c>
       <c r="C3" t="n">
-        <v>37.48</v>
+        <v>32.02</v>
       </c>
       <c r="D3" t="n">
         <v>2.04</v>
@@ -1718,10 +1718,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>51.8</v>
+        <v>52.77</v>
       </c>
       <c r="C3" t="n">
-        <v>49.15</v>
+        <v>41.39</v>
       </c>
       <c r="D3" t="n">
         <v>2.52</v>
@@ -1770,10 +1770,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>52.79</v>
+        <v>53.23</v>
       </c>
       <c r="C2" t="n">
-        <v>43</v>
+        <v>37.96</v>
       </c>
       <c r="D2" t="n">
         <v>1.46</v>
@@ -1786,10 +1786,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>52.25</v>
+        <v>52.81</v>
       </c>
       <c r="C3" t="n">
-        <v>41.25</v>
+        <v>39.31</v>
       </c>
       <c r="D3" t="n">
         <v>1.76</v>
@@ -1838,10 +1838,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>52.16</v>
+        <v>52.38</v>
       </c>
       <c r="C2" t="n">
-        <v>33</v>
+        <v>29.41</v>
       </c>
       <c r="D2" t="n">
         <v>2.05</v>
@@ -1854,10 +1854,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>52.84</v>
+        <v>53.48</v>
       </c>
       <c r="C3" t="n">
-        <v>47.95</v>
+        <v>43.9</v>
       </c>
       <c r="D3" t="n">
         <v>1.29</v>
